--- a/49897_Intercuenca_Alto_Maranon_IV/_raw_reportes_xlsx/IDConfig_67677_completo.xlsx
+++ b/49897_Intercuenca_Alto_Maranon_IV/_raw_reportes_xlsx/IDConfig_67677_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R18c97c31562a4eac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0f98fc0bfcfe4a57"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.1508</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.1067</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.6733</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.5457</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.4613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.0467</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.0876</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.8040</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.4875</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     85.8154</x:v>
+        <x:v>     98.7680</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    100.9888</x:v>
+        <x:v>    113.2321</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    102.0010</x:v>
+        <x:v>    114.1974</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49897_Intercuenca_Alto_Maranon_IV/_raw_reportes_xlsx/IDConfig_67677_completo.xlsx
+++ b/49897_Intercuenca_Alto_Maranon_IV/_raw_reportes_xlsx/IDConfig_67677_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0f98fc0bfcfe4a57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R42bec212db744e2d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.6611</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     44.9657</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     90.2124</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.5033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.5765</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     82.7970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.5033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     88.3575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.0679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.9242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    107.8678</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.9834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.4560</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.9242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    102.2857</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     93.9242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     91.1401</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    109.7298</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1849</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    120.9166</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1176</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     94.8525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.2427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.3927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.9449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.2427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.6189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.3927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.2427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     86.5033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.0191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.3927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     79.0935</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.5765</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.3927</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     78.1680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.6498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     78.1680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     87.4303</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     85.5765</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     83.7234</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.0679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     91.1401</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    104.1457</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    105.0759</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     92.9959</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.6498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     84.6498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     42.1508</x:v>
+        <x:v>     79.0935</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     43.1067</x:v>
+        <x:v>     84.6498</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     52.6733</x:v>
+        <x:v>     86.5033</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     55.5457</x:v>
+        <x:v>     84.6498</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     57.4613</x:v>
+        <x:v>     86.5033</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     67.0467</x:v>
+        <x:v>     90.2124</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     66.0876</x:v>
+        <x:v>     92.0679</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     72.8040</x:v>
+        <x:v>     87.4303</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     80.4875</x:v>
+        <x:v>     94.8525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     98.7680</x:v>
+        <x:v>    112.5242</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    113.2321</x:v>
+        <x:v>    126.5192</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    114.1974</x:v>
+        <x:v>    127.4536</x:v>
       </x:c>
     </x:row>
     <x:row>
